--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2453,6 +2453,126 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123326329</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lövfallsmossen, Igelfors, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545269</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6522418</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joakim Isaksson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123300513</v>
+        <v>123298802</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1536,26 +1536,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545293</v>
+        <v>545272</v>
       </c>
       <c r="R10" t="n">
-        <v>6522345</v>
+        <v>6522416</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,6 +1589,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1611,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298802</v>
+        <v>123298804</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1646,7 +1643,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1655,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545272</v>
+        <v>545381</v>
       </c>
       <c r="R11" t="n">
-        <v>6522416</v>
+        <v>6522308</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1718,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298804</v>
+        <v>123300513</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1753,22 +1750,26 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545381</v>
+        <v>545293</v>
       </c>
       <c r="R12" t="n">
-        <v>6522308</v>
+        <v>6522345</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1806,7 +1807,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2573,6 +2573,831 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123345007</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Marketorp OSO 880 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>545459</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6522225</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123344650</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Marketorp O 590 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>545185</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6522418</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123345018</v>
+      </c>
+      <c r="B22" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Marketorp OSO 880 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>545459</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6522225</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123344908</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Marketorp O 660 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>545257</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6522370</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123344719</v>
+      </c>
+      <c r="B24" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Marketorp O 540 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>545139</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6522420</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123344670</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Marketorp O 590 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>545185</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6522418</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123344711</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Marketorp O 540 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>545139</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6522420</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1501,7 +1501,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298802</v>
+        <v>123300513</v>
       </c>
       <c r="B10" t="n">
         <v>98365</v>
@@ -1536,22 +1536,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545272</v>
+        <v>545293</v>
       </c>
       <c r="R10" t="n">
-        <v>6522416</v>
+        <v>6522345</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1589,7 +1593,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1608,7 +1611,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298804</v>
+        <v>123298802</v>
       </c>
       <c r="B11" t="n">
         <v>98365</v>
@@ -1643,7 +1646,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1652,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545381</v>
+        <v>545272</v>
       </c>
       <c r="R11" t="n">
-        <v>6522308</v>
+        <v>6522416</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,7 +1718,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123300513</v>
+        <v>123298804</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1750,26 +1753,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545293</v>
+        <v>545381</v>
       </c>
       <c r="R12" t="n">
-        <v>6522345</v>
+        <v>6522308</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,6 +1806,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298800</v>
+        <v>123300513</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,22 +710,26 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545280</v>
+        <v>545293</v>
       </c>
       <c r="R2" t="n">
-        <v>6522415</v>
+        <v>6522345</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298814</v>
+        <v>123298812</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>92236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544991</v>
+        <v>545274</v>
       </c>
       <c r="R3" t="n">
-        <v>6522502</v>
+        <v>6522322</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298805</v>
+        <v>123298806</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>79387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545418</v>
+        <v>545408</v>
       </c>
       <c r="R4" t="n">
-        <v>6522224</v>
+        <v>6522248</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298812</v>
+        <v>123298800</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +1001,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545274</v>
+        <v>545280</v>
       </c>
       <c r="R5" t="n">
-        <v>6522322</v>
+        <v>6522415</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1070,6 +1077,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1088,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298809</v>
+        <v>123298810</v>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1108,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545351</v>
+        <v>545305</v>
       </c>
       <c r="R6" t="n">
-        <v>6522287</v>
+        <v>6522322</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1172,6 +1184,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298811</v>
+        <v>123298808</v>
       </c>
       <c r="B7" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1215,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545282</v>
+        <v>545372</v>
       </c>
       <c r="R7" t="n">
-        <v>6522327</v>
+        <v>6522273</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1274,6 +1291,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1292,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298801</v>
+        <v>123300511</v>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,41 +1322,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545279</v>
+        <v>545277</v>
       </c>
       <c r="R8" t="n">
-        <v>6522416</v>
+        <v>6522329</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1394,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298808</v>
+        <v>123298801</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,42 +1432,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545372</v>
+        <v>545279</v>
       </c>
       <c r="R9" t="n">
-        <v>6522273</v>
+        <v>6522416</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1482,7 +1504,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1501,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123300513</v>
+        <v>123298807</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,49 +1534,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545293</v>
+        <v>545377</v>
       </c>
       <c r="R10" t="n">
-        <v>6522345</v>
+        <v>6522271</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298802</v>
+        <v>123298809</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,42 +1636,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545272</v>
+        <v>545351</v>
       </c>
       <c r="R11" t="n">
-        <v>6522416</v>
+        <v>6522287</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1699,7 +1708,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1721,7 +1729,7 @@
         <v>123298804</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298810</v>
+        <v>123298811</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,42 +1845,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545305</v>
+        <v>545282</v>
       </c>
       <c r="R13" t="n">
-        <v>6522322</v>
+        <v>6522327</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1913,7 +1917,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1932,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123300511</v>
+        <v>123300512</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>91365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,46 +1947,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545277</v>
+        <v>545039</v>
       </c>
       <c r="R14" t="n">
-        <v>6522329</v>
+        <v>6522487</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2042,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298806</v>
+        <v>123298803</v>
       </c>
       <c r="B15" t="n">
-        <v>79384</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,38 +2049,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545408</v>
+        <v>545285</v>
       </c>
       <c r="R15" t="n">
-        <v>6522248</v>
+        <v>6522380</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,6 +2125,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298803</v>
+        <v>123298805</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,42 +2156,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545285</v>
+        <v>545418</v>
       </c>
       <c r="R16" t="n">
-        <v>6522380</v>
+        <v>6522224</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2232,7 +2228,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298807</v>
+        <v>123298802</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,38 +2258,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545377</v>
+        <v>545272</v>
       </c>
       <c r="R17" t="n">
-        <v>6522271</v>
+        <v>6522416</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2335,6 +2334,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123300512</v>
+        <v>123298814</v>
       </c>
       <c r="B18" t="n">
-        <v>91362</v>
+        <v>8441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545039</v>
+        <v>544991</v>
       </c>
       <c r="R18" t="n">
-        <v>6522487</v>
+        <v>6522502</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123345007</v>
+        <v>123344719</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,25 +2587,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,14 +2619,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R20" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344650</v>
+        <v>123344711</v>
       </c>
       <c r="B21" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,14 +2735,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545185</v>
+        <v>545139</v>
       </c>
       <c r="R21" t="n">
-        <v>6522418</v>
+        <v>6522420</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123345018</v>
+        <v>123345007</v>
       </c>
       <c r="B22" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344908</v>
+        <v>123344670</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,8 +2956,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2967,14 +2975,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545257</v>
+        <v>545185</v>
       </c>
       <c r="R23" t="n">
-        <v>6522370</v>
+        <v>6522418</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3007,6 +3015,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123344719</v>
+        <v>123344908</v>
       </c>
       <c r="B24" t="n">
-        <v>105471</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,46 +3064,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>545257</v>
       </c>
       <c r="R24" t="n">
-        <v>6522420</v>
+        <v>6522370</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3155,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123344670</v>
+        <v>123344650</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3167,40 +3180,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3247,11 +3252,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344711</v>
+        <v>123345018</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>105474</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,25 +3296,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,14 +3328,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R26" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123300513</v>
+        <v>123298800</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,26 +710,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545293</v>
+        <v>545280</v>
       </c>
       <c r="R2" t="n">
-        <v>6522345</v>
+        <v>6522415</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298812</v>
+        <v>123298809</v>
       </c>
       <c r="B3" t="n">
-        <v>92236</v>
+        <v>105476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545274</v>
+        <v>545351</v>
       </c>
       <c r="R3" t="n">
-        <v>6522322</v>
+        <v>6522287</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -887,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298806</v>
+        <v>123300512</v>
       </c>
       <c r="B4" t="n">
-        <v>79387</v>
+        <v>91367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545408</v>
+        <v>545039</v>
       </c>
       <c r="R4" t="n">
-        <v>6522248</v>
+        <v>6522487</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298800</v>
+        <v>123298804</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,7 +1021,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545280</v>
+        <v>545381</v>
       </c>
       <c r="R5" t="n">
-        <v>6522415</v>
+        <v>6522308</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1096,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298810</v>
+        <v>123298806</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>79389</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,42 +1105,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545305</v>
+        <v>545408</v>
       </c>
       <c r="R6" t="n">
-        <v>6522322</v>
+        <v>6522248</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1184,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298808</v>
+        <v>123300513</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,22 +1230,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545372</v>
+        <v>545293</v>
       </c>
       <c r="R7" t="n">
-        <v>6522273</v>
+        <v>6522345</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1313,7 +1308,7 @@
         <v>123300511</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298801</v>
+        <v>123298802</v>
       </c>
       <c r="B9" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,35 +1427,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545279</v>
+        <v>545272</v>
       </c>
       <c r="R9" t="n">
         <v>6522416</v>
@@ -1504,6 +1503,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298807</v>
+        <v>123298805</v>
       </c>
       <c r="B10" t="n">
-        <v>105474</v>
+        <v>92238</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545377</v>
+        <v>545418</v>
       </c>
       <c r="R10" t="n">
-        <v>6522271</v>
+        <v>6522224</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298809</v>
+        <v>123298811</v>
       </c>
       <c r="B11" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545351</v>
+        <v>545282</v>
       </c>
       <c r="R11" t="n">
-        <v>6522287</v>
+        <v>6522327</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298804</v>
+        <v>123298814</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>8441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,42 +1738,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545381</v>
+        <v>544991</v>
       </c>
       <c r="R12" t="n">
-        <v>6522308</v>
+        <v>6522502</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1814,7 +1810,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1833,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298811</v>
+        <v>123298801</v>
       </c>
       <c r="B13" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545282</v>
+        <v>545279</v>
       </c>
       <c r="R13" t="n">
-        <v>6522327</v>
+        <v>6522416</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1935,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123300512</v>
+        <v>123298810</v>
       </c>
       <c r="B14" t="n">
-        <v>91365</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,41 +1942,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545039</v>
+        <v>545305</v>
       </c>
       <c r="R14" t="n">
-        <v>6522487</v>
+        <v>6522322</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,6 +2018,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298803</v>
+        <v>123298807</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,42 +2049,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545285</v>
+        <v>545377</v>
       </c>
       <c r="R15" t="n">
-        <v>6522380</v>
+        <v>6522271</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2125,7 +2121,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298805</v>
+        <v>123298812</v>
       </c>
       <c r="B16" t="n">
-        <v>92236</v>
+        <v>92238</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2184,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545418</v>
+        <v>545274</v>
       </c>
       <c r="R16" t="n">
-        <v>6522224</v>
+        <v>6522322</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2246,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298802</v>
+        <v>123298808</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,7 +2276,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2290,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545272</v>
+        <v>545372</v>
       </c>
       <c r="R17" t="n">
-        <v>6522416</v>
+        <v>6522273</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2353,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298814</v>
+        <v>123298803</v>
       </c>
       <c r="B18" t="n">
-        <v>8441</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,38 +2360,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544991</v>
+        <v>545285</v>
       </c>
       <c r="R18" t="n">
-        <v>6522502</v>
+        <v>6522380</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2437,6 +2436,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344719</v>
+        <v>123344711</v>
       </c>
       <c r="B20" t="n">
-        <v>105474</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,25 +2587,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344711</v>
+        <v>123344670</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,25 +2724,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545139</v>
+        <v>545185</v>
       </c>
       <c r="R21" t="n">
-        <v>6522420</v>
+        <v>6522418</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2775,6 +2783,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2807,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123345007</v>
+        <v>123344719</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>105476</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,25 +2832,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2851,14 +2864,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2923,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344670</v>
+        <v>123344908</v>
       </c>
       <c r="B23" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,16 +2969,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2975,14 +2980,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545185</v>
+        <v>545257</v>
       </c>
       <c r="R23" t="n">
-        <v>6522418</v>
+        <v>6522370</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,11 +3020,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123344908</v>
+        <v>123345007</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545257</v>
+        <v>545459</v>
       </c>
       <c r="R24" t="n">
-        <v>6522370</v>
+        <v>6522225</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3171,7 +3171,7 @@
         <v>123344650</v>
       </c>
       <c r="B25" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>123345018</v>
       </c>
       <c r="B26" t="n">
-        <v>105474</v>
+        <v>105476</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1624,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298811</v>
+        <v>123298814</v>
       </c>
       <c r="B11" t="n">
-        <v>105476</v>
+        <v>8441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,21 +1640,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545282</v>
+        <v>544991</v>
       </c>
       <c r="R11" t="n">
-        <v>6522327</v>
+        <v>6522502</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298814</v>
+        <v>123298811</v>
       </c>
       <c r="B12" t="n">
-        <v>8441</v>
+        <v>105476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,21 +1742,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544991</v>
+        <v>545282</v>
       </c>
       <c r="R12" t="n">
-        <v>6522502</v>
+        <v>6522327</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123344719</v>
+        <v>123344908</v>
       </c>
       <c r="B22" t="n">
-        <v>105476</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,46 +2832,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>545257</v>
       </c>
       <c r="R22" t="n">
-        <v>6522420</v>
+        <v>6522370</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344908</v>
+        <v>123344719</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>105476</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,46 +2948,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545257</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>6522370</v>
+        <v>6522420</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298800</v>
+        <v>123298802</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545280</v>
+        <v>545272</v>
       </c>
       <c r="R2" t="n">
-        <v>6522415</v>
+        <v>6522416</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298809</v>
+        <v>123298814</v>
       </c>
       <c r="B3" t="n">
-        <v>105476</v>
+        <v>8441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545351</v>
+        <v>544991</v>
       </c>
       <c r="R3" t="n">
-        <v>6522287</v>
+        <v>6522502</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300512</v>
+        <v>123298805</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>92244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545039</v>
+        <v>545418</v>
       </c>
       <c r="R4" t="n">
-        <v>6522487</v>
+        <v>6522224</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298804</v>
+        <v>123300511</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,22 +1021,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545381</v>
+        <v>545277</v>
       </c>
       <c r="R5" t="n">
-        <v>6522308</v>
+        <v>6522329</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298806</v>
+        <v>123298804</v>
       </c>
       <c r="B6" t="n">
-        <v>79389</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,38 +1108,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545408</v>
+        <v>545381</v>
       </c>
       <c r="R6" t="n">
-        <v>6522248</v>
+        <v>6522308</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1177,6 +1184,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123300513</v>
+        <v>123300512</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>91373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,46 +1215,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545293</v>
+        <v>545039</v>
       </c>
       <c r="R7" t="n">
-        <v>6522345</v>
+        <v>6522487</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123300511</v>
+        <v>123298812</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>92244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,49 +1317,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545277</v>
+        <v>545274</v>
       </c>
       <c r="R8" t="n">
-        <v>6522329</v>
+        <v>6522322</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298802</v>
+        <v>123298806</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>79390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1427,42 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545272</v>
+        <v>545408</v>
       </c>
       <c r="R9" t="n">
-        <v>6522416</v>
+        <v>6522248</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,7 +1491,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1522,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298805</v>
+        <v>123298809</v>
       </c>
       <c r="B10" t="n">
-        <v>92238</v>
+        <v>105482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545418</v>
+        <v>545351</v>
       </c>
       <c r="R10" t="n">
-        <v>6522224</v>
+        <v>6522287</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1624,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298814</v>
+        <v>123298807</v>
       </c>
       <c r="B11" t="n">
-        <v>8441</v>
+        <v>105482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,21 +1627,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1664,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544991</v>
+        <v>545377</v>
       </c>
       <c r="R11" t="n">
-        <v>6522502</v>
+        <v>6522271</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1726,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298811</v>
+        <v>123298803</v>
       </c>
       <c r="B12" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,38 +1725,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545282</v>
+        <v>545285</v>
       </c>
       <c r="R12" t="n">
-        <v>6522327</v>
+        <v>6522380</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,6 +1801,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1828,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298801</v>
+        <v>123298810</v>
       </c>
       <c r="B13" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1840,38 +1832,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545279</v>
+        <v>545305</v>
       </c>
       <c r="R13" t="n">
-        <v>6522416</v>
+        <v>6522322</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1912,6 +1908,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1930,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298810</v>
+        <v>123298800</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,7 +1962,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1974,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545305</v>
+        <v>545280</v>
       </c>
       <c r="R14" t="n">
-        <v>6522322</v>
+        <v>6522415</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2037,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298807</v>
+        <v>123298801</v>
       </c>
       <c r="B15" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545377</v>
+        <v>545279</v>
       </c>
       <c r="R15" t="n">
-        <v>6522271</v>
+        <v>6522416</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2139,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298812</v>
+        <v>123300513</v>
       </c>
       <c r="B16" t="n">
-        <v>92238</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,41 +2148,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545274</v>
+        <v>545293</v>
       </c>
       <c r="R16" t="n">
-        <v>6522322</v>
+        <v>6522345</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,7 +2249,7 @@
         <v>123298808</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2348,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298803</v>
+        <v>123298811</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,42 +2365,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545285</v>
+        <v>545282</v>
       </c>
       <c r="R18" t="n">
-        <v>6522380</v>
+        <v>6522327</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2436,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344711</v>
+        <v>123344670</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,25 +2608,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545139</v>
+        <v>545185</v>
       </c>
       <c r="R20" t="n">
-        <v>6522420</v>
+        <v>6522418</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2659,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344670</v>
+        <v>123345018</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>105482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,54 +2716,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545185</v>
+        <v>545459</v>
       </c>
       <c r="R21" t="n">
-        <v>6522418</v>
+        <v>6522225</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2783,11 +2788,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123344908</v>
+        <v>123344711</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2857,21 +2857,21 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545257</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>6522370</v>
+        <v>6522420</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2939,7 +2939,7 @@
         <v>123344719</v>
       </c>
       <c r="B23" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123345007</v>
+        <v>123344908</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545459</v>
+        <v>545257</v>
       </c>
       <c r="R24" t="n">
-        <v>6522225</v>
+        <v>6522370</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3171,7 +3171,7 @@
         <v>123344650</v>
       </c>
       <c r="B25" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123345018</v>
+        <v>123345007</v>
       </c>
       <c r="B26" t="n">
-        <v>105476</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,25 +3296,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298802</v>
+        <v>123298800</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545272</v>
+        <v>545280</v>
       </c>
       <c r="R2" t="n">
-        <v>6522416</v>
+        <v>6522415</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298814</v>
+        <v>123298802</v>
       </c>
       <c r="B3" t="n">
-        <v>8441</v>
+        <v>98379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +794,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544991</v>
+        <v>545272</v>
       </c>
       <c r="R3" t="n">
-        <v>6522502</v>
+        <v>6522416</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -866,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298805</v>
+        <v>123298806</v>
       </c>
       <c r="B4" t="n">
-        <v>92244</v>
+        <v>79393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545418</v>
+        <v>545408</v>
       </c>
       <c r="R4" t="n">
-        <v>6522224</v>
+        <v>6522248</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300511</v>
+        <v>123298803</v>
       </c>
       <c r="B5" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,26 +1026,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545277</v>
+        <v>545285</v>
       </c>
       <c r="R5" t="n">
-        <v>6522329</v>
+        <v>6522380</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,6 +1079,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1096,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298804</v>
+        <v>123298810</v>
       </c>
       <c r="B6" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1140,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545381</v>
+        <v>545305</v>
       </c>
       <c r="R6" t="n">
-        <v>6522308</v>
+        <v>6522322</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1203,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123300512</v>
+        <v>123298804</v>
       </c>
       <c r="B7" t="n">
-        <v>91373</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1217,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545039</v>
+        <v>545381</v>
       </c>
       <c r="R7" t="n">
-        <v>6522487</v>
+        <v>6522308</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,6 +1293,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298812</v>
+        <v>123298809</v>
       </c>
       <c r="B8" t="n">
-        <v>92244</v>
+        <v>105485</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545274</v>
+        <v>545351</v>
       </c>
       <c r="R8" t="n">
-        <v>6522322</v>
+        <v>6522287</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298806</v>
+        <v>123300513</v>
       </c>
       <c r="B9" t="n">
-        <v>79390</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,41 +1426,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545408</v>
+        <v>545293</v>
       </c>
       <c r="R9" t="n">
-        <v>6522248</v>
+        <v>6522345</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1509,10 +1524,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298809</v>
+        <v>123298805</v>
       </c>
       <c r="B10" t="n">
-        <v>105482</v>
+        <v>92247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1540,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545351</v>
+        <v>545418</v>
       </c>
       <c r="R10" t="n">
-        <v>6522287</v>
+        <v>6522224</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1611,10 +1626,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298807</v>
+        <v>123298812</v>
       </c>
       <c r="B11" t="n">
-        <v>105482</v>
+        <v>92247</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,21 +1642,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1651,10 +1666,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545377</v>
+        <v>545274</v>
       </c>
       <c r="R11" t="n">
-        <v>6522271</v>
+        <v>6522322</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1713,10 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298803</v>
+        <v>123298807</v>
       </c>
       <c r="B12" t="n">
-        <v>98376</v>
+        <v>105485</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,42 +1740,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545285</v>
+        <v>545377</v>
       </c>
       <c r="R12" t="n">
-        <v>6522380</v>
+        <v>6522271</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1801,7 +1812,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1820,10 +1830,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298810</v>
+        <v>123300512</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>91376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,45 +1842,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545305</v>
+        <v>545039</v>
       </c>
       <c r="R13" t="n">
-        <v>6522322</v>
+        <v>6522487</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,7 +1914,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1932,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298800</v>
+        <v>123300511</v>
       </c>
       <c r="B14" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,22 +1967,26 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545280</v>
+        <v>545277</v>
       </c>
       <c r="R14" t="n">
-        <v>6522415</v>
+        <v>6522329</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,7 +2024,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2034,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298801</v>
+        <v>123298814</v>
       </c>
       <c r="B15" t="n">
-        <v>105482</v>
+        <v>8441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2050,21 +2058,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2074,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545279</v>
+        <v>544991</v>
       </c>
       <c r="R15" t="n">
-        <v>6522416</v>
+        <v>6522502</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2136,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123300513</v>
+        <v>123298808</v>
       </c>
       <c r="B16" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2171,26 +2179,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545293</v>
+        <v>545372</v>
       </c>
       <c r="R16" t="n">
-        <v>6522345</v>
+        <v>6522273</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2228,6 +2232,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2246,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298808</v>
+        <v>123298811</v>
       </c>
       <c r="B17" t="n">
-        <v>98376</v>
+        <v>105485</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,42 +2263,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545372</v>
+        <v>545282</v>
       </c>
       <c r="R17" t="n">
-        <v>6522273</v>
+        <v>6522327</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2334,7 +2335,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298811</v>
+        <v>123298801</v>
       </c>
       <c r="B18" t="n">
-        <v>105482</v>
+        <v>105485</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545282</v>
+        <v>545279</v>
       </c>
       <c r="R18" t="n">
-        <v>6522327</v>
+        <v>6522416</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344670</v>
+        <v>123345007</v>
       </c>
       <c r="B20" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,33 +2608,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545185</v>
+        <v>545459</v>
       </c>
       <c r="R20" t="n">
-        <v>6522418</v>
+        <v>6522225</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,11 +2659,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123345018</v>
+        <v>123344711</v>
       </c>
       <c r="B21" t="n">
-        <v>105482</v>
+        <v>98379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2703,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,14 +2735,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R21" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2820,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123344711</v>
+        <v>123345018</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>105485</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,14 +2851,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R22" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2936,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344719</v>
+        <v>123344670</v>
       </c>
       <c r="B23" t="n">
-        <v>105482</v>
+        <v>98379</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,46 +2935,54 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545139</v>
+        <v>545185</v>
       </c>
       <c r="R23" t="n">
-        <v>6522420</v>
+        <v>6522418</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3020,6 +3015,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3055,7 @@
         <v>123344908</v>
       </c>
       <c r="B24" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>123344650</v>
       </c>
       <c r="B25" t="n">
-        <v>105482</v>
+        <v>105485</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123345007</v>
+        <v>123344719</v>
       </c>
       <c r="B26" t="n">
-        <v>98376</v>
+        <v>105485</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,25 +3296,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3328,14 +3328,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R26" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298809</v>
+        <v>123300513</v>
       </c>
       <c r="B8" t="n">
-        <v>105485</v>
+        <v>98379</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,41 +1324,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545351</v>
+        <v>545293</v>
       </c>
       <c r="R8" t="n">
-        <v>6522287</v>
+        <v>6522345</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123300513</v>
+        <v>123298809</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>105485</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,49 +1434,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545293</v>
+        <v>545351</v>
       </c>
       <c r="R9" t="n">
-        <v>6522345</v>
+        <v>6522287</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298800</v>
+        <v>123298802</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545280</v>
+        <v>545272</v>
       </c>
       <c r="R2" t="n">
-        <v>6522415</v>
+        <v>6522416</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298802</v>
+        <v>123298804</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545272</v>
+        <v>545381</v>
       </c>
       <c r="R3" t="n">
-        <v>6522416</v>
+        <v>6522308</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298806</v>
+        <v>123298800</v>
       </c>
       <c r="B4" t="n">
-        <v>79393</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,38 +901,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545408</v>
+        <v>545280</v>
       </c>
       <c r="R4" t="n">
-        <v>6522248</v>
+        <v>6522415</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -973,6 +977,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298803</v>
+        <v>123300512</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>91393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,45 +1008,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545285</v>
+        <v>545039</v>
       </c>
       <c r="R5" t="n">
-        <v>6522380</v>
+        <v>6522487</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,7 +1080,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298810</v>
+        <v>123298809</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,42 +1110,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545305</v>
+        <v>545351</v>
       </c>
       <c r="R6" t="n">
-        <v>6522322</v>
+        <v>6522287</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1186,7 +1182,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298804</v>
+        <v>123298810</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,7 +1235,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545381</v>
+        <v>545305</v>
       </c>
       <c r="R7" t="n">
-        <v>6522308</v>
+        <v>6522322</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123300513</v>
+        <v>123298806</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>79399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,49 +1319,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545293</v>
+        <v>545408</v>
       </c>
       <c r="R8" t="n">
-        <v>6522345</v>
+        <v>6522248</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298809</v>
+        <v>123300511</v>
       </c>
       <c r="B9" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,41 +1421,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545351</v>
+        <v>545277</v>
       </c>
       <c r="R9" t="n">
-        <v>6522287</v>
+        <v>6522329</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298805</v>
+        <v>123298811</v>
       </c>
       <c r="B10" t="n">
-        <v>92247</v>
+        <v>105502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1540,21 +1535,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1564,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545418</v>
+        <v>545282</v>
       </c>
       <c r="R10" t="n">
-        <v>6522224</v>
+        <v>6522327</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1629,7 +1624,7 @@
         <v>123298807</v>
       </c>
       <c r="B11" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123300512</v>
+        <v>123298805</v>
       </c>
       <c r="B12" t="n">
-        <v>91376</v>
+        <v>92264</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1768,13 +1763,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545039</v>
+        <v>545418</v>
       </c>
       <c r="R12" t="n">
-        <v>6522487</v>
+        <v>6522224</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1830,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298812</v>
+        <v>123298814</v>
       </c>
       <c r="B13" t="n">
-        <v>92247</v>
+        <v>8445</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,21 +1841,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1870,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545274</v>
+        <v>544991</v>
       </c>
       <c r="R13" t="n">
-        <v>6522322</v>
+        <v>6522502</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1932,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123300511</v>
+        <v>123298801</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,49 +1939,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545277</v>
+        <v>545279</v>
       </c>
       <c r="R14" t="n">
-        <v>6522329</v>
+        <v>6522416</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2042,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298814</v>
+        <v>123298808</v>
       </c>
       <c r="B15" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,38 +2041,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544991</v>
+        <v>545372</v>
       </c>
       <c r="R15" t="n">
-        <v>6522502</v>
+        <v>6522273</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2126,6 +2117,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298808</v>
+        <v>123298812</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>92264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,42 +2148,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545372</v>
+        <v>545274</v>
       </c>
       <c r="R16" t="n">
-        <v>6522273</v>
+        <v>6522322</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2232,7 +2220,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298811</v>
+        <v>123298803</v>
       </c>
       <c r="B17" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,38 +2250,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545282</v>
+        <v>545285</v>
       </c>
       <c r="R17" t="n">
-        <v>6522327</v>
+        <v>6522380</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2335,6 +2326,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2353,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298801</v>
+        <v>123300513</v>
       </c>
       <c r="B18" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,41 +2357,49 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545279</v>
+        <v>545293</v>
       </c>
       <c r="R18" t="n">
-        <v>6522416</v>
+        <v>6522345</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>123345007</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344711</v>
+        <v>123344650</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,14 +2735,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545139</v>
+        <v>545185</v>
       </c>
       <c r="R21" t="n">
-        <v>6522420</v>
+        <v>6522418</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123345018</v>
+        <v>123344711</v>
       </c>
       <c r="B22" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2851,14 +2851,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2926,7 +2926,7 @@
         <v>123344670</v>
       </c>
       <c r="B23" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123344908</v>
+        <v>123345018</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>105502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,46 +3064,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545257</v>
+        <v>545459</v>
       </c>
       <c r="R24" t="n">
-        <v>6522370</v>
+        <v>6522225</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123344650</v>
+        <v>123344719</v>
       </c>
       <c r="B25" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3212,14 +3212,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545185</v>
+        <v>545139</v>
       </c>
       <c r="R25" t="n">
-        <v>6522418</v>
+        <v>6522420</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344719</v>
+        <v>123344908</v>
       </c>
       <c r="B26" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,46 +3296,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545139</v>
+        <v>545257</v>
       </c>
       <c r="R26" t="n">
-        <v>6522420</v>
+        <v>6522370</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298801</v>
+        <v>123298812</v>
       </c>
       <c r="B14" t="n">
-        <v>105502</v>
+        <v>92264</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545279</v>
+        <v>545274</v>
       </c>
       <c r="R14" t="n">
-        <v>6522416</v>
+        <v>6522322</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298808</v>
+        <v>123298801</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,42 +2041,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545372</v>
+        <v>545279</v>
       </c>
       <c r="R15" t="n">
-        <v>6522273</v>
+        <v>6522416</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,7 +2113,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298812</v>
+        <v>123298808</v>
       </c>
       <c r="B16" t="n">
-        <v>92264</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,38 +2143,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545274</v>
+        <v>545372</v>
       </c>
       <c r="R16" t="n">
-        <v>6522322</v>
+        <v>6522273</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,6 +2219,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298803</v>
+        <v>123300513</v>
       </c>
       <c r="B17" t="n">
         <v>98396</v>
@@ -2273,22 +2273,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545285</v>
+        <v>545293</v>
       </c>
       <c r="R17" t="n">
-        <v>6522380</v>
+        <v>6522345</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2326,7 +2330,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2345,7 +2348,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123300513</v>
+        <v>123298803</v>
       </c>
       <c r="B18" t="n">
         <v>98396</v>
@@ -2380,26 +2383,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545293</v>
+        <v>545285</v>
       </c>
       <c r="R18" t="n">
-        <v>6522345</v>
+        <v>6522380</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,6 +2436,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298812</v>
+        <v>123298801</v>
       </c>
       <c r="B14" t="n">
-        <v>92264</v>
+        <v>105502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545274</v>
+        <v>545279</v>
       </c>
       <c r="R14" t="n">
-        <v>6522322</v>
+        <v>6522416</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298801</v>
+        <v>123298808</v>
       </c>
       <c r="B15" t="n">
-        <v>105502</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,38 +2041,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545279</v>
+        <v>545372</v>
       </c>
       <c r="R15" t="n">
-        <v>6522416</v>
+        <v>6522273</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2113,6 +2117,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2131,10 +2136,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298808</v>
+        <v>123298812</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>92264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,42 +2148,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545372</v>
+        <v>545274</v>
       </c>
       <c r="R16" t="n">
-        <v>6522273</v>
+        <v>6522322</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2219,7 +2220,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123300513</v>
+        <v>123298803</v>
       </c>
       <c r="B17" t="n">
         <v>98396</v>
@@ -2273,26 +2273,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545293</v>
+        <v>545285</v>
       </c>
       <c r="R17" t="n">
-        <v>6522345</v>
+        <v>6522380</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,6 +2326,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2348,7 +2345,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298803</v>
+        <v>123300513</v>
       </c>
       <c r="B18" t="n">
         <v>98396</v>
@@ -2383,22 +2380,26 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545285</v>
+        <v>545293</v>
       </c>
       <c r="R18" t="n">
-        <v>6522380</v>
+        <v>6522345</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2436,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298801</v>
+        <v>123298812</v>
       </c>
       <c r="B14" t="n">
-        <v>105502</v>
+        <v>92264</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1943,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545279</v>
+        <v>545274</v>
       </c>
       <c r="R14" t="n">
-        <v>6522416</v>
+        <v>6522322</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,10 +2029,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298808</v>
+        <v>123298801</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>105502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,42 +2041,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545372</v>
+        <v>545279</v>
       </c>
       <c r="R15" t="n">
-        <v>6522273</v>
+        <v>6522416</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2117,7 +2113,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298812</v>
+        <v>123298808</v>
       </c>
       <c r="B16" t="n">
-        <v>92264</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,38 +2143,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545274</v>
+        <v>545372</v>
       </c>
       <c r="R16" t="n">
-        <v>6522322</v>
+        <v>6522273</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2220,6 +2219,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298802</v>
+        <v>123298801</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545272</v>
+        <v>545279</v>
       </c>
       <c r="R2" t="n">
         <v>6522416</v>
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298804</v>
+        <v>123298806</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545381</v>
+        <v>545408</v>
       </c>
       <c r="R3" t="n">
-        <v>6522308</v>
+        <v>6522248</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -870,7 +861,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298800</v>
+        <v>123298812</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,42 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545280</v>
+        <v>545274</v>
       </c>
       <c r="R4" t="n">
-        <v>6522415</v>
+        <v>6522322</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -977,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123300512</v>
+        <v>123298805</v>
       </c>
       <c r="B5" t="n">
-        <v>91393</v>
+        <v>92269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545039</v>
+        <v>545418</v>
       </c>
       <c r="R5" t="n">
-        <v>6522487</v>
+        <v>6522224</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298809</v>
+        <v>123298803</v>
       </c>
       <c r="B6" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,38 +1095,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545351</v>
+        <v>545285</v>
       </c>
       <c r="R6" t="n">
-        <v>6522287</v>
+        <v>6522380</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1182,6 +1171,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298810</v>
+        <v>123298802</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,7 +1225,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1244,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545305</v>
+        <v>545272</v>
       </c>
       <c r="R7" t="n">
-        <v>6522322</v>
+        <v>6522416</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298806</v>
+        <v>123298804</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,38 +1309,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545408</v>
+        <v>545381</v>
       </c>
       <c r="R8" t="n">
-        <v>6522248</v>
+        <v>6522308</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1391,6 +1385,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123300511</v>
+        <v>123298814</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>8447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,49 +1416,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545277</v>
+        <v>544991</v>
       </c>
       <c r="R9" t="n">
-        <v>6522329</v>
+        <v>6522502</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1519,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298811</v>
+        <v>123300512</v>
       </c>
       <c r="B10" t="n">
-        <v>105502</v>
+        <v>91398</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545282</v>
+        <v>545039</v>
       </c>
       <c r="R10" t="n">
-        <v>6522327</v>
+        <v>6522487</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1624,7 +1611,7 @@
         <v>123298807</v>
       </c>
       <c r="B11" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298805</v>
+        <v>123298800</v>
       </c>
       <c r="B12" t="n">
-        <v>92264</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,38 +1722,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545418</v>
+        <v>545280</v>
       </c>
       <c r="R12" t="n">
-        <v>6522224</v>
+        <v>6522415</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1807,6 +1798,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298814</v>
+        <v>123298810</v>
       </c>
       <c r="B13" t="n">
-        <v>8445</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,38 +1829,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544991</v>
+        <v>545305</v>
       </c>
       <c r="R13" t="n">
-        <v>6522502</v>
+        <v>6522322</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1909,6 +1905,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1927,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298812</v>
+        <v>123298809</v>
       </c>
       <c r="B14" t="n">
-        <v>92264</v>
+        <v>105518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1967,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545274</v>
+        <v>545351</v>
       </c>
       <c r="R14" t="n">
-        <v>6522322</v>
+        <v>6522287</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2029,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298801</v>
+        <v>123298811</v>
       </c>
       <c r="B15" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2069,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545279</v>
+        <v>545282</v>
       </c>
       <c r="R15" t="n">
-        <v>6522416</v>
+        <v>6522327</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2131,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298808</v>
+        <v>123300513</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,22 +2163,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545372</v>
+        <v>545293</v>
       </c>
       <c r="R16" t="n">
-        <v>6522273</v>
+        <v>6522345</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,7 +2220,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2238,10 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298803</v>
+        <v>123300511</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2273,22 +2273,26 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545285</v>
+        <v>545277</v>
       </c>
       <c r="R17" t="n">
-        <v>6522380</v>
+        <v>6522329</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2326,7 +2330,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2345,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123300513</v>
+        <v>123298808</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2380,26 +2383,22 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545293</v>
+        <v>545372</v>
       </c>
       <c r="R18" t="n">
-        <v>6522345</v>
+        <v>6522273</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,6 +2436,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123345007</v>
+        <v>123344670</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,25 +2608,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545459</v>
+        <v>545185</v>
       </c>
       <c r="R20" t="n">
-        <v>6522225</v>
+        <v>6522418</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2659,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344650</v>
+        <v>123344711</v>
       </c>
       <c r="B21" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2735,14 +2748,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545185</v>
+        <v>545139</v>
       </c>
       <c r="R21" t="n">
-        <v>6522418</v>
+        <v>6522420</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2807,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123344711</v>
+        <v>123345007</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,14 +2864,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R22" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2923,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344670</v>
+        <v>123344650</v>
       </c>
       <c r="B23" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,40 +2948,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3015,11 +3020,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3055,7 @@
         <v>123345018</v>
       </c>
       <c r="B24" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>123344719</v>
       </c>
       <c r="B25" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>123344908</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298801</v>
+        <v>123298812</v>
       </c>
       <c r="B2" t="n">
-        <v>105518</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545279</v>
+        <v>545274</v>
       </c>
       <c r="R2" t="n">
-        <v>6522416</v>
+        <v>6522322</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298806</v>
+        <v>123298800</v>
       </c>
       <c r="B3" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545408</v>
+        <v>545280</v>
       </c>
       <c r="R3" t="n">
-        <v>6522248</v>
+        <v>6522415</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,6 +865,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298812</v>
+        <v>123300513</v>
       </c>
       <c r="B4" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +896,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545274</v>
+        <v>545293</v>
       </c>
       <c r="R4" t="n">
-        <v>6522322</v>
+        <v>6522345</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298805</v>
+        <v>123298810</v>
       </c>
       <c r="B5" t="n">
-        <v>92269</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +1006,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545418</v>
+        <v>545305</v>
       </c>
       <c r="R5" t="n">
-        <v>6522224</v>
+        <v>6522322</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1065,6 +1082,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298803</v>
+        <v>123298806</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,42 +1113,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545285</v>
+        <v>545408</v>
       </c>
       <c r="R6" t="n">
-        <v>6522380</v>
+        <v>6522248</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1171,7 +1185,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298802</v>
+        <v>123300512</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>91400</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,45 +1215,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545272</v>
+        <v>545039</v>
       </c>
       <c r="R7" t="n">
-        <v>6522416</v>
+        <v>6522487</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1278,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298804</v>
+        <v>123298801</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,42 +1317,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545381</v>
+        <v>545279</v>
       </c>
       <c r="R8" t="n">
-        <v>6522308</v>
+        <v>6522416</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1385,7 +1389,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1404,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298814</v>
+        <v>123298809</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>105520</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544991</v>
+        <v>545351</v>
       </c>
       <c r="R9" t="n">
-        <v>6522502</v>
+        <v>6522287</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1506,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123300512</v>
+        <v>123300511</v>
       </c>
       <c r="B10" t="n">
-        <v>91398</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1521,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545039</v>
+        <v>545277</v>
       </c>
       <c r="R10" t="n">
-        <v>6522487</v>
+        <v>6522329</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1608,10 +1619,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298807</v>
+        <v>123298803</v>
       </c>
       <c r="B11" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,38 +1631,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545377</v>
+        <v>545285</v>
       </c>
       <c r="R11" t="n">
-        <v>6522271</v>
+        <v>6522380</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1692,6 +1707,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1710,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298800</v>
+        <v>123298805</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>92271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,42 +1738,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545280</v>
+        <v>545418</v>
       </c>
       <c r="R12" t="n">
-        <v>6522415</v>
+        <v>6522224</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1798,7 +1810,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1817,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298810</v>
+        <v>123298807</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,42 +1840,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545305</v>
+        <v>545377</v>
       </c>
       <c r="R13" t="n">
-        <v>6522322</v>
+        <v>6522271</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1905,7 +1912,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1924,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298809</v>
+        <v>123298802</v>
       </c>
       <c r="B14" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,38 +1942,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545351</v>
+        <v>545272</v>
       </c>
       <c r="R14" t="n">
-        <v>6522287</v>
+        <v>6522416</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2008,6 +2018,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2026,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298811</v>
+        <v>123298814</v>
       </c>
       <c r="B15" t="n">
-        <v>105518</v>
+        <v>8447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545282</v>
+        <v>544991</v>
       </c>
       <c r="R15" t="n">
-        <v>6522327</v>
+        <v>6522502</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2128,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123300513</v>
+        <v>123298804</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2163,26 +2174,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545293</v>
+        <v>545381</v>
       </c>
       <c r="R16" t="n">
-        <v>6522345</v>
+        <v>6522308</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2220,6 +2227,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2238,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123300511</v>
+        <v>123298811</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,49 +2258,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545277</v>
+        <v>545282</v>
       </c>
       <c r="R17" t="n">
-        <v>6522329</v>
+        <v>6522327</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>123298808</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344670</v>
+        <v>123345007</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,33 +2608,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545185</v>
+        <v>545459</v>
       </c>
       <c r="R20" t="n">
-        <v>6522418</v>
+        <v>6522225</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,11 +2659,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344711</v>
+        <v>123344719</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2703,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2820,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123345007</v>
+        <v>123344711</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2864,14 +2851,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2936,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344650</v>
+        <v>123344670</v>
       </c>
       <c r="B23" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,32 +2935,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3020,6 +3015,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3055,7 +3055,7 @@
         <v>123345018</v>
       </c>
       <c r="B24" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123344719</v>
+        <v>123344908</v>
       </c>
       <c r="B25" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3180,46 +3180,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545139</v>
+        <v>545257</v>
       </c>
       <c r="R25" t="n">
-        <v>6522420</v>
+        <v>6522370</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344908</v>
+        <v>123344650</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>105520</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,46 +3296,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545257</v>
+        <v>545185</v>
       </c>
       <c r="R26" t="n">
-        <v>6522370</v>
+        <v>6522418</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298812</v>
+        <v>123298800</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545274</v>
+        <v>545280</v>
       </c>
       <c r="R2" t="n">
-        <v>6522322</v>
+        <v>6522415</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298800</v>
+        <v>123298812</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545280</v>
+        <v>545274</v>
       </c>
       <c r="R3" t="n">
-        <v>6522415</v>
+        <v>6522322</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -865,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298800</v>
+        <v>123298812</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545280</v>
+        <v>545274</v>
       </c>
       <c r="R2" t="n">
-        <v>6522415</v>
+        <v>6522322</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298812</v>
+        <v>123298800</v>
       </c>
       <c r="B3" t="n">
-        <v>92271</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545274</v>
+        <v>545280</v>
       </c>
       <c r="R3" t="n">
-        <v>6522322</v>
+        <v>6522415</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -866,6 +865,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298812</v>
+        <v>123298810</v>
       </c>
       <c r="B2" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545274</v>
+        <v>545305</v>
       </c>
       <c r="R2" t="n">
         <v>6522322</v>
@@ -759,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298800</v>
+        <v>123300513</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,22 +817,26 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545280</v>
+        <v>545293</v>
       </c>
       <c r="R3" t="n">
-        <v>6522415</v>
+        <v>6522345</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +874,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123300513</v>
+        <v>123298806</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,49 +904,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545293</v>
+        <v>545408</v>
       </c>
       <c r="R4" t="n">
-        <v>6522345</v>
+        <v>6522248</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298810</v>
+        <v>123298811</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,42 +1006,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545305</v>
+        <v>545282</v>
       </c>
       <c r="R5" t="n">
-        <v>6522322</v>
+        <v>6522327</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,7 +1078,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298806</v>
+        <v>123298802</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,38 +1108,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545408</v>
+        <v>545272</v>
       </c>
       <c r="R6" t="n">
-        <v>6522248</v>
+        <v>6522416</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1185,6 +1184,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123300512</v>
+        <v>123298804</v>
       </c>
       <c r="B7" t="n">
-        <v>91400</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,41 +1215,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545039</v>
+        <v>545381</v>
       </c>
       <c r="R7" t="n">
-        <v>6522487</v>
+        <v>6522308</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,6 +1291,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1308,7 +1313,7 @@
         <v>123298801</v>
       </c>
       <c r="B8" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298809</v>
+        <v>123298807</v>
       </c>
       <c r="B9" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545351</v>
+        <v>545377</v>
       </c>
       <c r="R9" t="n">
-        <v>6522287</v>
+        <v>6522271</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1512,7 +1517,7 @@
         <v>123300511</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298803</v>
+        <v>123298800</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,7 +1659,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545285</v>
+        <v>545280</v>
       </c>
       <c r="R11" t="n">
-        <v>6522380</v>
+        <v>6522415</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1828,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298807</v>
+        <v>123298809</v>
       </c>
       <c r="B13" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,10 +1873,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545377</v>
+        <v>545351</v>
       </c>
       <c r="R13" t="n">
-        <v>6522271</v>
+        <v>6522287</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1930,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298802</v>
+        <v>123298814</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>8447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1942,42 +1947,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545272</v>
+        <v>544991</v>
       </c>
       <c r="R14" t="n">
-        <v>6522416</v>
+        <v>6522502</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2018,7 +2019,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298814</v>
+        <v>123298812</v>
       </c>
       <c r="B15" t="n">
-        <v>8447</v>
+        <v>92271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544991</v>
+        <v>545274</v>
       </c>
       <c r="R15" t="n">
-        <v>6522502</v>
+        <v>6522322</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298804</v>
+        <v>123298808</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545381</v>
+        <v>545372</v>
       </c>
       <c r="R16" t="n">
-        <v>6522308</v>
+        <v>6522273</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298811</v>
+        <v>123298803</v>
       </c>
       <c r="B17" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,38 +2258,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545282</v>
+        <v>545285</v>
       </c>
       <c r="R17" t="n">
-        <v>6522327</v>
+        <v>6522380</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2330,6 +2334,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2348,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298808</v>
+        <v>123300512</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>91400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,45 +2365,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545372</v>
+        <v>545039</v>
       </c>
       <c r="R18" t="n">
-        <v>6522273</v>
+        <v>6522487</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2436,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>123326329</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123345007</v>
+        <v>123344670</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2608,25 +2608,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545459</v>
+        <v>545185</v>
       </c>
       <c r="R20" t="n">
-        <v>6522225</v>
+        <v>6522418</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2659,6 +2667,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344719</v>
+        <v>123345018</v>
       </c>
       <c r="B21" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,14 +2748,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R21" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2810,7 +2823,7 @@
         <v>123344711</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2923,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344670</v>
+        <v>123345007</v>
       </c>
       <c r="B23" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2956,33 +2969,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545185</v>
+        <v>545459</v>
       </c>
       <c r="R23" t="n">
-        <v>6522418</v>
+        <v>6522225</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,11 +3020,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123345018</v>
+        <v>123344719</v>
       </c>
       <c r="B24" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3096,14 +3096,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R24" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123344908</v>
+        <v>123344650</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3180,46 +3180,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545257</v>
+        <v>545185</v>
       </c>
       <c r="R25" t="n">
-        <v>6522370</v>
+        <v>6522418</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344650</v>
+        <v>123344908</v>
       </c>
       <c r="B26" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,46 +3296,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545185</v>
+        <v>545257</v>
       </c>
       <c r="R26" t="n">
-        <v>6522418</v>
+        <v>6522370</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1310,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298801</v>
+        <v>123300511</v>
       </c>
       <c r="B8" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,41 +1322,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545279</v>
+        <v>545277</v>
       </c>
       <c r="R8" t="n">
-        <v>6522416</v>
+        <v>6522329</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1420,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298807</v>
+        <v>123298801</v>
       </c>
       <c r="B9" t="n">
         <v>105095</v>
@@ -1452,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545377</v>
+        <v>545279</v>
       </c>
       <c r="R9" t="n">
-        <v>6522271</v>
+        <v>6522416</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1514,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123300511</v>
+        <v>123298807</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,49 +1534,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545277</v>
+        <v>545377</v>
       </c>
       <c r="R10" t="n">
-        <v>6522329</v>
+        <v>6522271</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298810</v>
+        <v>123298806</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545305</v>
+        <v>545408</v>
       </c>
       <c r="R2" t="n">
-        <v>6522322</v>
+        <v>6522248</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -763,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300513</v>
+        <v>123300512</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>91400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545293</v>
+        <v>545039</v>
       </c>
       <c r="R3" t="n">
-        <v>6522345</v>
+        <v>6522487</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -892,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298806</v>
+        <v>123298811</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>105095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545408</v>
+        <v>545282</v>
       </c>
       <c r="R4" t="n">
-        <v>6522248</v>
+        <v>6522327</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -994,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298811</v>
+        <v>123298809</v>
       </c>
       <c r="B5" t="n">
         <v>105095</v>
@@ -1034,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545282</v>
+        <v>545351</v>
       </c>
       <c r="R5" t="n">
-        <v>6522327</v>
+        <v>6522287</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1096,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298802</v>
+        <v>123300511</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1131,22 +1118,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545272</v>
+        <v>545277</v>
       </c>
       <c r="R6" t="n">
-        <v>6522416</v>
+        <v>6522329</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,7 +1175,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1203,7 +1193,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298804</v>
+        <v>123298800</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1238,7 +1228,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1247,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545381</v>
+        <v>545280</v>
       </c>
       <c r="R7" t="n">
-        <v>6522308</v>
+        <v>6522415</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1310,7 +1300,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123300511</v>
+        <v>123298802</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1345,26 +1335,22 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545277</v>
+        <v>545272</v>
       </c>
       <c r="R8" t="n">
-        <v>6522329</v>
+        <v>6522416</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1402,6 +1388,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298801</v>
+        <v>123298812</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545279</v>
+        <v>545274</v>
       </c>
       <c r="R9" t="n">
-        <v>6522416</v>
+        <v>6522322</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1522,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298807</v>
+        <v>123298805</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>92271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545377</v>
+        <v>545418</v>
       </c>
       <c r="R10" t="n">
-        <v>6522271</v>
+        <v>6522224</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1624,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298800</v>
+        <v>123298801</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,42 +1623,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545280</v>
+        <v>545279</v>
       </c>
       <c r="R11" t="n">
-        <v>6522415</v>
+        <v>6522416</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1712,7 +1695,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,10 +1713,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298805</v>
+        <v>123298810</v>
       </c>
       <c r="B12" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,38 +1725,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545418</v>
+        <v>545305</v>
       </c>
       <c r="R12" t="n">
-        <v>6522224</v>
+        <v>6522322</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1815,6 +1801,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1833,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298809</v>
+        <v>123298808</v>
       </c>
       <c r="B13" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,38 +1832,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545351</v>
+        <v>545372</v>
       </c>
       <c r="R13" t="n">
-        <v>6522287</v>
+        <v>6522273</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1917,6 +1908,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1935,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298814</v>
+        <v>123298803</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,38 +1939,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544991</v>
+        <v>545285</v>
       </c>
       <c r="R14" t="n">
-        <v>6522502</v>
+        <v>6522380</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2019,6 +2015,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2037,10 +2034,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298812</v>
+        <v>123298807</v>
       </c>
       <c r="B15" t="n">
-        <v>92271</v>
+        <v>105095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2050,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2074,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545274</v>
+        <v>545377</v>
       </c>
       <c r="R15" t="n">
-        <v>6522322</v>
+        <v>6522271</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2139,7 +2136,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298808</v>
+        <v>123300513</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2174,22 +2171,26 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545372</v>
+        <v>545293</v>
       </c>
       <c r="R16" t="n">
-        <v>6522273</v>
+        <v>6522345</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2227,7 +2228,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2246,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298803</v>
+        <v>123298814</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,42 +2258,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545285</v>
+        <v>544991</v>
       </c>
       <c r="R17" t="n">
-        <v>6522380</v>
+        <v>6522502</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2334,7 +2330,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2353,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123300512</v>
+        <v>123298804</v>
       </c>
       <c r="B18" t="n">
-        <v>91400</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,41 +2360,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545039</v>
+        <v>545381</v>
       </c>
       <c r="R18" t="n">
-        <v>6522487</v>
+        <v>6522308</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2437,6 +2436,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2575,7 +2575,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344670</v>
+        <v>123344908</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2608,16 +2608,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -2627,14 +2619,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545185</v>
+        <v>545257</v>
       </c>
       <c r="R20" t="n">
-        <v>6522418</v>
+        <v>6522370</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,11 +2659,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2704,7 +2691,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123345018</v>
+        <v>123344719</v>
       </c>
       <c r="B21" t="n">
         <v>105095</v>
@@ -2748,14 +2735,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R21" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2820,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123344711</v>
+        <v>123345018</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2832,25 +2819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2864,14 +2851,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R22" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2936,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123345007</v>
+        <v>123344650</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,25 +2935,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2980,14 +2967,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545459</v>
+        <v>545185</v>
       </c>
       <c r="R23" t="n">
-        <v>6522225</v>
+        <v>6522418</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3052,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123344719</v>
+        <v>123344711</v>
       </c>
       <c r="B24" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,25 +3051,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123344650</v>
+        <v>123345007</v>
       </c>
       <c r="B25" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3180,25 +3167,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3212,14 +3199,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545185</v>
+        <v>545459</v>
       </c>
       <c r="R25" t="n">
-        <v>6522418</v>
+        <v>6522225</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3284,7 +3271,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344908</v>
+        <v>123344670</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3317,8 +3304,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3328,14 +3323,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545257</v>
+        <v>545185</v>
       </c>
       <c r="R26" t="n">
-        <v>6522370</v>
+        <v>6522418</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3368,6 +3363,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298806</v>
+        <v>123298811</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>105095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545408</v>
+        <v>545282</v>
       </c>
       <c r="R2" t="n">
-        <v>6522248</v>
+        <v>6522327</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123300512</v>
+        <v>123298809</v>
       </c>
       <c r="B3" t="n">
-        <v>91400</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545039</v>
+        <v>545351</v>
       </c>
       <c r="R3" t="n">
-        <v>6522487</v>
+        <v>6522287</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298811</v>
+        <v>123298804</v>
       </c>
       <c r="B4" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545282</v>
+        <v>545381</v>
       </c>
       <c r="R4" t="n">
-        <v>6522327</v>
+        <v>6522308</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -963,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123298809</v>
+        <v>123300513</v>
       </c>
       <c r="B5" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +998,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545351</v>
+        <v>545293</v>
       </c>
       <c r="R5" t="n">
-        <v>6522287</v>
+        <v>6522345</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123300511</v>
+        <v>123298805</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,49 +1108,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545277</v>
+        <v>545418</v>
       </c>
       <c r="R6" t="n">
-        <v>6522329</v>
+        <v>6522224</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123298800</v>
+        <v>123298801</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,42 +1210,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545280</v>
+        <v>545279</v>
       </c>
       <c r="R7" t="n">
-        <v>6522415</v>
+        <v>6522416</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,7 +1282,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298802</v>
+        <v>123298808</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545272</v>
+        <v>545372</v>
       </c>
       <c r="R8" t="n">
-        <v>6522416</v>
+        <v>6522273</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298812</v>
+        <v>123298803</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,38 +1419,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545274</v>
+        <v>545285</v>
       </c>
       <c r="R9" t="n">
-        <v>6522322</v>
+        <v>6522380</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1491,6 +1495,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1509,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123298805</v>
+        <v>123300511</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,41 +1526,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545418</v>
+        <v>545277</v>
       </c>
       <c r="R10" t="n">
-        <v>6522224</v>
+        <v>6522329</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298801</v>
+        <v>123298810</v>
       </c>
       <c r="B11" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,38 +1636,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545279</v>
+        <v>545305</v>
       </c>
       <c r="R11" t="n">
-        <v>6522416</v>
+        <v>6522322</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1695,6 +1712,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1713,7 +1731,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298810</v>
+        <v>123298802</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1748,7 +1766,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1757,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545305</v>
+        <v>545272</v>
       </c>
       <c r="R12" t="n">
-        <v>6522322</v>
+        <v>6522416</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1820,7 +1838,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298808</v>
+        <v>123298800</v>
       </c>
       <c r="B13" t="n">
         <v>98079</v>
@@ -1855,7 +1873,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1864,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545372</v>
+        <v>545280</v>
       </c>
       <c r="R13" t="n">
-        <v>6522273</v>
+        <v>6522415</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1927,10 +1945,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298803</v>
+        <v>123298812</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,42 +1957,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545285</v>
+        <v>545274</v>
       </c>
       <c r="R14" t="n">
-        <v>6522380</v>
+        <v>6522322</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2015,7 +2029,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2136,10 +2149,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123300513</v>
+        <v>123298814</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,49 +2161,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545293</v>
+        <v>544991</v>
       </c>
       <c r="R16" t="n">
-        <v>6522345</v>
+        <v>6522502</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2246,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298814</v>
+        <v>123298806</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>79406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2286,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544991</v>
+        <v>545408</v>
       </c>
       <c r="R17" t="n">
-        <v>6522502</v>
+        <v>6522248</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2348,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123298804</v>
+        <v>123300512</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>91400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,45 +2365,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545381</v>
+        <v>545039</v>
       </c>
       <c r="R18" t="n">
-        <v>6522308</v>
+        <v>6522487</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2436,7 +2437,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2575,7 +2575,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344908</v>
+        <v>123344711</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2612,21 +2612,21 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545257</v>
+        <v>545139</v>
       </c>
       <c r="R20" t="n">
-        <v>6522370</v>
+        <v>6522420</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344719</v>
+        <v>123344650</v>
       </c>
       <c r="B21" t="n">
         <v>105095</v>
@@ -2735,14 +2735,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545139</v>
+        <v>545185</v>
       </c>
       <c r="R21" t="n">
-        <v>6522420</v>
+        <v>6522418</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344650</v>
+        <v>123344670</v>
       </c>
       <c r="B23" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,32 +2935,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3007,6 +3015,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3039,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123344711</v>
+        <v>123344719</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,25 +3064,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,7 +3284,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344670</v>
+        <v>123344908</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3304,16 +3317,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>vinterståndare</t>
@@ -3323,14 +3328,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545185</v>
+        <v>545257</v>
       </c>
       <c r="R26" t="n">
-        <v>6522418</v>
+        <v>6522370</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3363,11 +3368,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123298811</v>
+        <v>123298803</v>
       </c>
       <c r="B2" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545282</v>
+        <v>545285</v>
       </c>
       <c r="R2" t="n">
-        <v>6522327</v>
+        <v>6522380</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -759,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123298809</v>
+        <v>123298814</v>
       </c>
       <c r="B3" t="n">
-        <v>105095</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545351</v>
+        <v>544991</v>
       </c>
       <c r="R3" t="n">
-        <v>6522287</v>
+        <v>6522502</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123298804</v>
+        <v>123300511</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -914,22 +919,26 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545381</v>
+        <v>545277</v>
       </c>
       <c r="R4" t="n">
-        <v>6522308</v>
+        <v>6522329</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1096,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123298805</v>
+        <v>123298800</v>
       </c>
       <c r="B6" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,38 +1116,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545418</v>
+        <v>545280</v>
       </c>
       <c r="R6" t="n">
-        <v>6522224</v>
+        <v>6522415</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,6 +1192,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1300,7 +1313,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123298808</v>
+        <v>123298804</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1335,7 +1348,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1344,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545372</v>
+        <v>545381</v>
       </c>
       <c r="R8" t="n">
-        <v>6522273</v>
+        <v>6522308</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,10 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123298803</v>
+        <v>123300512</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>91400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,45 +1432,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545285</v>
+        <v>545039</v>
       </c>
       <c r="R9" t="n">
-        <v>6522380</v>
+        <v>6522487</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,7 +1504,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1514,7 +1522,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123300511</v>
+        <v>123298802</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1549,26 +1557,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>179</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545277</v>
+        <v>545272</v>
       </c>
       <c r="R10" t="n">
-        <v>6522329</v>
+        <v>6522416</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,6 +1610,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1624,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123298810</v>
+        <v>123298809</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,42 +1641,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545305</v>
+        <v>545351</v>
       </c>
       <c r="R11" t="n">
-        <v>6522322</v>
+        <v>6522287</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1712,7 +1713,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123298802</v>
+        <v>123298811</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,42 +1743,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545272</v>
+        <v>545282</v>
       </c>
       <c r="R12" t="n">
-        <v>6522416</v>
+        <v>6522327</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1819,7 +1815,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1838,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298800</v>
+        <v>123298806</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1850,42 +1845,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545280</v>
+        <v>545408</v>
       </c>
       <c r="R13" t="n">
-        <v>6522415</v>
+        <v>6522248</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1926,7 +1917,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1945,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298812</v>
+        <v>123298810</v>
       </c>
       <c r="B14" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1957,35 +1947,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545274</v>
+        <v>545305</v>
       </c>
       <c r="R14" t="n">
         <v>6522322</v>
@@ -2029,6 +2023,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2047,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123298807</v>
+        <v>123298805</v>
       </c>
       <c r="B15" t="n">
-        <v>105095</v>
+        <v>92271</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2063,21 +2058,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2087,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545377</v>
+        <v>545418</v>
       </c>
       <c r="R15" t="n">
-        <v>6522271</v>
+        <v>6522224</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2149,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123298814</v>
+        <v>123298808</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2161,38 +2156,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544991</v>
+        <v>545372</v>
       </c>
       <c r="R16" t="n">
-        <v>6522502</v>
+        <v>6522273</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2233,6 +2232,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2251,10 +2251,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123298806</v>
+        <v>123298807</v>
       </c>
       <c r="B17" t="n">
-        <v>79406</v>
+        <v>105095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,25 +2263,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545408</v>
+        <v>545377</v>
       </c>
       <c r="R17" t="n">
-        <v>6522248</v>
+        <v>6522271</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2353,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123300512</v>
+        <v>123298812</v>
       </c>
       <c r="B18" t="n">
-        <v>91400</v>
+        <v>92271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545039</v>
+        <v>545274</v>
       </c>
       <c r="R18" t="n">
-        <v>6522487</v>
+        <v>6522322</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344711</v>
+        <v>123344650</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,25 +2587,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,14 +2619,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545139</v>
+        <v>545185</v>
       </c>
       <c r="R20" t="n">
-        <v>6522420</v>
+        <v>6522418</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344650</v>
+        <v>123344908</v>
       </c>
       <c r="B21" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,46 +2703,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545185</v>
+        <v>545257</v>
       </c>
       <c r="R21" t="n">
-        <v>6522418</v>
+        <v>6522370</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123345018</v>
+        <v>123344711</v>
       </c>
       <c r="B22" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2851,14 +2851,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545459</v>
+        <v>545139</v>
       </c>
       <c r="R22" t="n">
-        <v>6522225</v>
+        <v>6522420</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3052,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123344719</v>
+        <v>123345007</v>
       </c>
       <c r="B24" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,25 +3064,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3096,14 +3096,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R24" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123345007</v>
+        <v>123345018</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3180,25 +3180,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3284,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344908</v>
+        <v>123344719</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3296,46 +3296,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545257</v>
+        <v>545139</v>
       </c>
       <c r="R26" t="n">
-        <v>6522370</v>
+        <v>6522420</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123298806</v>
+        <v>123298810</v>
       </c>
       <c r="B13" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,38 +1845,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545408</v>
+        <v>545305</v>
       </c>
       <c r="R13" t="n">
-        <v>6522248</v>
+        <v>6522322</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1917,6 +1921,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1935,10 +1940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123298810</v>
+        <v>123298806</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,42 +1952,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545305</v>
+        <v>545408</v>
       </c>
       <c r="R14" t="n">
-        <v>6522322</v>
+        <v>6522248</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2023,7 +2024,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -2575,10 +2575,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123344650</v>
+        <v>123345007</v>
       </c>
       <c r="B20" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,25 +2587,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,14 +2619,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545185</v>
+        <v>545459</v>
       </c>
       <c r="R20" t="n">
-        <v>6522418</v>
+        <v>6522225</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123344908</v>
+        <v>123344719</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2703,46 +2703,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Marketorp O 660 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545257</v>
+        <v>545139</v>
       </c>
       <c r="R21" t="n">
-        <v>6522370</v>
+        <v>6522420</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2807,7 +2807,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123344711</v>
+        <v>123344908</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -2844,21 +2844,21 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp O 660 m, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545139</v>
+        <v>545257</v>
       </c>
       <c r="R22" t="n">
-        <v>6522420</v>
+        <v>6522370</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123344670</v>
+        <v>123344711</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -2956,33 +2956,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Marketorp O 590 m, Ög</t>
+          <t>Marketorp O 540 m, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>545185</v>
+        <v>545139</v>
       </c>
       <c r="R23" t="n">
-        <v>6522418</v>
+        <v>6522420</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3015,11 +3007,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123345007</v>
+        <v>123344650</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3064,25 +3051,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3096,14 +3083,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545459</v>
+        <v>545185</v>
       </c>
       <c r="R24" t="n">
-        <v>6522225</v>
+        <v>6522418</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3168,10 +3155,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123345018</v>
+        <v>123344670</v>
       </c>
       <c r="B25" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3180,46 +3167,54 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Marketorp OSO 880 m, Ög</t>
+          <t>Marketorp O 590 m, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545459</v>
+        <v>545185</v>
       </c>
       <c r="R25" t="n">
-        <v>6522225</v>
+        <v>6522418</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3252,6 +3247,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Över 100 ex, spridda</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3284,7 +3284,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123344719</v>
+        <v>123345018</v>
       </c>
       <c r="B26" t="n">
         <v>105095</v>
@@ -3328,14 +3328,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Marketorp O 540 m, Ög</t>
+          <t>Marketorp OSO 880 m, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545139</v>
+        <v>545459</v>
       </c>
       <c r="R26" t="n">
-        <v>6522420</v>
+        <v>6522225</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -785,12 +785,7 @@
         <v>123298814</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,6 +811,15 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lövfallsmossen, Ög</t>
@@ -866,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3403,6 +3403,356 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129866950</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lövfallsmossen, N, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>545378</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6522291</v>
+      </c>
+      <c r="S27" t="n">
+        <v>26</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>E-Fin-0625</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Två rapporter</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129866949</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lövfallsmossen, N, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>545283</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6522344</v>
+      </c>
+      <c r="S28" t="n">
+        <v>36</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>E-Fin-0626</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>4 rapporter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129866951</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Dammkärret, SV, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>545285</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6522388</v>
+      </c>
+      <c r="S29" t="n">
+        <v>34</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Finspång</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Regna</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>E-Fin-0624</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Sammanslagning av 4 rapporter</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -3408,7 +3408,7 @@
         <v>129866950</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129866949</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>129866951</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -3408,7 +3408,7 @@
         <v>129866950</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129866949</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>129866951</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>123298814</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>129866950</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129866949</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>129866951</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -3408,7 +3408,7 @@
         <v>129866950</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129866949</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>129866951</v>
       </c>
       <c r="B29" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 5550-2025 artfynd.xlsx
+++ b/artfynd/A 5550-2025 artfynd.xlsx
@@ -3408,7 +3408,7 @@
         <v>129866950</v>
       </c>
       <c r="B27" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>129866949</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         <v>129866951</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
